--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/KANSAS_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/KANSAS_2014.xlsx
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C99">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C217">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C225">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C505">
@@ -10104,7 +10104,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C542">
@@ -14892,7 +14892,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C808">
